--- a/tax_manager/arrear.xlsx
+++ b/tax_manager/arrear.xlsx
@@ -1,31 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\taxapp\tax_manager\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5347B91-F4B2-4A34-9C4C-6B18716F1DF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54BE24A1-AE66-471F-8A83-A86AB5CF931F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="56">
   <si>
     <t>TIN</t>
   </si>
@@ -48,35 +60,158 @@
     <t>Collection</t>
   </si>
   <si>
-    <t>2023-2024</t>
-  </si>
-  <si>
-    <t>2018-2019</t>
-  </si>
-  <si>
-    <t>2019-2020</t>
-  </si>
-  <si>
-    <t>2020-2021</t>
-  </si>
-  <si>
-    <t>2021-2022</t>
-  </si>
-  <si>
-    <t>813916210887</t>
-  </si>
-  <si>
-    <t>মিজ লুৎফুন্নাহার আজাদ</t>
-  </si>
-  <si>
-    <t>কাজল রানী ভৌমিক</t>
+    <t>#</t>
+  </si>
+  <si>
+    <t>Name, Address &amp; TIN</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Assessment Year</t>
+  </si>
+  <si>
+    <t>Arrear</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Action</t>
+  </si>
+  <si>
+    <t>মৃত খালেকুজ্জামান মজুমদার</t>
+  </si>
+  <si>
+    <t>পিতা মৃত রফিকুল হক মজুমদার</t>
+  </si>
+  <si>
+    <t>ননা মিয়া হাজী বাড়ী,দক্ষিণ আধার মানিক</t>
+  </si>
+  <si>
+    <t>ছাগলনাইয়া,ফেনী</t>
+  </si>
+  <si>
+    <t>disputed</t>
+  </si>
+  <si>
+    <t>2003-2004</t>
+  </si>
+  <si>
+    <t>undisputed</t>
+  </si>
+  <si>
+    <t>1999-2000</t>
+  </si>
+  <si>
+    <t>1998-1999</t>
+  </si>
+  <si>
+    <t>1,63,893</t>
+  </si>
+  <si>
+    <t>1,35,000</t>
+  </si>
+  <si>
+    <t>1997-1998</t>
+  </si>
+  <si>
+    <t>1,61,151</t>
+  </si>
+  <si>
+    <t>1988-1989</t>
+  </si>
+  <si>
+    <t>1,89,123</t>
+  </si>
+  <si>
+    <t>1989-1990</t>
+  </si>
+  <si>
+    <t>1,98,996</t>
+  </si>
+  <si>
+    <t>1990-1991</t>
+  </si>
+  <si>
+    <t>1,98,951</t>
+  </si>
+  <si>
+    <t>1991-1992</t>
+  </si>
+  <si>
+    <t>1,62,001</t>
+  </si>
+  <si>
+    <t>1992-1993</t>
+  </si>
+  <si>
+    <t>1,41,743</t>
+  </si>
+  <si>
+    <t>1993-1994</t>
+  </si>
+  <si>
+    <t>1,50,056</t>
+  </si>
+  <si>
+    <t>1994-1995</t>
+  </si>
+  <si>
+    <t>1,46,336</t>
+  </si>
+  <si>
+    <t>1995-1996</t>
+  </si>
+  <si>
+    <t>1,12,310</t>
+  </si>
+  <si>
+    <t>1996-1997</t>
+  </si>
+  <si>
+    <t>2002-2003</t>
+  </si>
+  <si>
+    <t>2004-2005</t>
+  </si>
+  <si>
+    <t>2006-2007</t>
+  </si>
+  <si>
+    <t>2007-2008</t>
+  </si>
+  <si>
+    <t>2008-2009</t>
+  </si>
+  <si>
+    <t>2009-2010</t>
+  </si>
+  <si>
+    <t>2010-2011</t>
+  </si>
+  <si>
+    <t>2011-2012</t>
+  </si>
+  <si>
+    <t>2012-2013</t>
+  </si>
+  <si>
+    <t>2013-2014</t>
+  </si>
+  <si>
+    <t>1987-1988</t>
+  </si>
+  <si>
+    <t>খালেকুজ্জামান মজুমদার</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -90,8 +225,15 @@
       <name val="Source Sans Pro"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF212529"/>
+      <name val="Source Sans Pro"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -104,8 +246,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -128,64 +276,160 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFDEE2E6"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFDEE2E6"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFDEE2E6"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFDEE2E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFDEE2E6"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFDEE2E6"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFDEE2E6"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFDEE2E6"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFDEE2E6"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFDEE2E6"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFDEE2E6"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFDEE2E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFDEE2E6"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFDEE2E6"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFDEE2E6"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="FFDEE2E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FFDEE2E6"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFDEE2E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFDEE2E6"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFDEE2E6"/>
+      </right>
+      <top style="thick">
+        <color rgb="FFDEE2E6"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -461,17 +705,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.85546875" customWidth="1"/>
+    <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -494,125 +739,925 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
-        <v>597960426452</v>
-      </c>
-      <c r="B2" s="1" t="s">
+    <row r="2" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="12">
+        <v>554777563324</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="15">
+        <v>28893</v>
+      </c>
+      <c r="E2" s="13">
+        <v>0</v>
+      </c>
+      <c r="F2" s="17">
+        <f>D2+E2</f>
+        <v>28893</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="12">
+        <v>554777563324</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="15">
+        <v>121151</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0</v>
+      </c>
+      <c r="F3" s="17">
+        <f t="shared" ref="F3:F14" si="0">D3+E3</f>
+        <v>121151</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="12">
+        <v>554777563324</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="16">
+        <v>189123</v>
+      </c>
+      <c r="E4" s="13">
+        <v>0</v>
+      </c>
+      <c r="F4" s="17">
+        <f t="shared" si="0"/>
+        <v>189123</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="12">
+        <v>554777563324</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="16">
+        <v>198996</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0</v>
+      </c>
+      <c r="F5" s="17">
+        <f t="shared" si="0"/>
+        <v>198996</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="12">
+        <v>554777563324</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="16">
+        <v>198951</v>
+      </c>
+      <c r="E6" s="13">
+        <v>0</v>
+      </c>
+      <c r="F6" s="17">
+        <f t="shared" si="0"/>
+        <v>198951</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="12">
+        <v>554777563324</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="16">
+        <v>162001</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0</v>
+      </c>
+      <c r="F7" s="17">
+        <f t="shared" si="0"/>
+        <v>162001</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="12">
+        <v>554777563324</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="15">
+        <v>80243</v>
+      </c>
+      <c r="E8" s="13">
+        <v>0</v>
+      </c>
+      <c r="F8" s="17">
+        <f t="shared" si="0"/>
+        <v>80243</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="12">
+        <v>554777563324</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="15">
+        <v>115056</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0</v>
+      </c>
+      <c r="F9" s="17">
+        <f t="shared" si="0"/>
+        <v>115056</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="12">
+        <v>554777563324</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="15">
+        <v>112676</v>
+      </c>
+      <c r="E10" s="13">
+        <v>0</v>
+      </c>
+      <c r="F10" s="17">
+        <f t="shared" si="0"/>
+        <v>112676</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="12">
+        <v>554777563324</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" s="15">
+        <v>84310</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0</v>
+      </c>
+      <c r="F11" s="17">
+        <f t="shared" si="0"/>
+        <v>84310</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="12">
+        <v>554777563324</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" s="15">
+        <v>86774</v>
+      </c>
+      <c r="E12" s="13">
+        <v>0</v>
+      </c>
+      <c r="F12" s="17">
+        <f t="shared" si="0"/>
+        <v>86774</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="12">
+        <v>554777563324</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="15">
+        <v>3188</v>
+      </c>
+      <c r="E13" s="1">
+        <v>0</v>
+      </c>
+      <c r="F13" s="17">
+        <f t="shared" si="0"/>
+        <v>3188</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="12">
+        <v>554777563324</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" s="15">
+        <v>1557</v>
+      </c>
+      <c r="E14" s="13">
+        <v>0</v>
+      </c>
+      <c r="F14" s="17">
+        <f t="shared" si="0"/>
+        <v>1557</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4E19FBD-C233-4B27-8608-9FE6CE07F647}">
+  <dimension ref="A1:I25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:9" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="64.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="18">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2">
-        <v>3059</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>3059</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="3">
-        <v>7900</v>
-      </c>
-      <c r="E3" s="4">
-        <v>0</v>
-      </c>
-      <c r="F3" s="5">
-        <v>7900</v>
-      </c>
-      <c r="G3" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="3">
-        <v>7800</v>
-      </c>
-      <c r="E4" s="4">
-        <v>0</v>
-      </c>
-      <c r="F4" s="5">
-        <v>7800</v>
-      </c>
-      <c r="G4" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="3">
-        <v>6900</v>
-      </c>
-      <c r="E5" s="4">
-        <v>0</v>
-      </c>
-      <c r="F5" s="5">
-        <v>6900</v>
-      </c>
-      <c r="G5" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="3">
-        <v>8340</v>
-      </c>
-      <c r="E6" s="4">
-        <v>0</v>
-      </c>
-      <c r="F6" s="5">
-        <v>8340</v>
-      </c>
-      <c r="G6" s="4">
-        <v>0</v>
-      </c>
+      <c r="C2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="7">
+        <v>2538</v>
+      </c>
+      <c r="F2" s="8">
+        <v>0</v>
+      </c>
+      <c r="G2" s="7">
+        <v>2538</v>
+      </c>
+      <c r="H2" s="7">
+        <v>2538</v>
+      </c>
+      <c r="I2" s="6"/>
+    </row>
+    <row r="3" spans="1:9" ht="63.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="19"/>
+      <c r="B3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="7">
+        <v>2316</v>
+      </c>
+      <c r="F3" s="8">
+        <v>0</v>
+      </c>
+      <c r="G3" s="7">
+        <v>2316</v>
+      </c>
+      <c r="H3" s="7">
+        <v>2316</v>
+      </c>
+      <c r="I3" s="6"/>
+    </row>
+    <row r="4" spans="1:9" ht="79.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="19"/>
+      <c r="B4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="8">
+        <v>0</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I4" s="6"/>
+    </row>
+    <row r="5" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="19"/>
+      <c r="B5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="8">
+        <v>0</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="7">
+        <v>40000</v>
+      </c>
+      <c r="I5" s="6"/>
+    </row>
+    <row r="6" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="19"/>
+      <c r="B6" s="4">
+        <v>554777563324</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="8">
+        <v>0</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" s="8">
+        <v>0</v>
+      </c>
+      <c r="I6" s="6"/>
+    </row>
+    <row r="7" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="19"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" s="8">
+        <v>0</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="H7" s="8">
+        <v>0</v>
+      </c>
+      <c r="I7" s="6"/>
+    </row>
+    <row r="8" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="19"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F8" s="8">
+        <v>0</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="H8" s="8">
+        <v>0</v>
+      </c>
+      <c r="I8" s="6"/>
+    </row>
+    <row r="9" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="19"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9" s="8">
+        <v>0</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="H9" s="8">
+        <v>0</v>
+      </c>
+      <c r="I9" s="6"/>
+    </row>
+    <row r="10" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="19"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F10" s="8">
+        <v>0</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="H10" s="7">
+        <v>61500</v>
+      </c>
+      <c r="I10" s="6"/>
+    </row>
+    <row r="11" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="19"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F11" s="8">
+        <v>0</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H11" s="7">
+        <v>35000</v>
+      </c>
+      <c r="I11" s="6"/>
+    </row>
+    <row r="12" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="19"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F12" s="8">
+        <v>0</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="H12" s="7">
+        <v>33660</v>
+      </c>
+      <c r="I12" s="6"/>
+    </row>
+    <row r="13" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="19"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F13" s="8">
+        <v>0</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="H13" s="7">
+        <v>28000</v>
+      </c>
+      <c r="I13" s="6"/>
+    </row>
+    <row r="14" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="19"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" s="7">
+        <v>86774</v>
+      </c>
+      <c r="F14" s="8">
+        <v>0</v>
+      </c>
+      <c r="G14" s="7">
+        <v>86774</v>
+      </c>
+      <c r="H14" s="8">
+        <v>0</v>
+      </c>
+      <c r="I14" s="6"/>
+    </row>
+    <row r="15" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="19"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E15" s="7">
+        <v>3188</v>
+      </c>
+      <c r="F15" s="8">
+        <v>0</v>
+      </c>
+      <c r="G15" s="7">
+        <v>3188</v>
+      </c>
+      <c r="H15" s="8">
+        <v>0</v>
+      </c>
+      <c r="I15" s="6"/>
+    </row>
+    <row r="16" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="19"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="E16" s="7">
+        <v>1557</v>
+      </c>
+      <c r="F16" s="8">
+        <v>0</v>
+      </c>
+      <c r="G16" s="7">
+        <v>1557</v>
+      </c>
+      <c r="H16" s="8">
+        <v>0</v>
+      </c>
+      <c r="I16" s="6"/>
+    </row>
+    <row r="17" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="19"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E17" s="8">
+        <v>0</v>
+      </c>
+      <c r="F17" s="7">
+        <v>2500</v>
+      </c>
+      <c r="G17" s="7">
+        <v>2500</v>
+      </c>
+      <c r="H17" s="7">
+        <v>2500</v>
+      </c>
+      <c r="I17" s="6"/>
+    </row>
+    <row r="18" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="19"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E18" s="8">
+        <v>0</v>
+      </c>
+      <c r="F18" s="7">
+        <v>1000</v>
+      </c>
+      <c r="G18" s="7">
+        <v>1000</v>
+      </c>
+      <c r="H18" s="7">
+        <v>1000</v>
+      </c>
+      <c r="I18" s="6"/>
+    </row>
+    <row r="19" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="19"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E19" s="8">
+        <v>0</v>
+      </c>
+      <c r="F19" s="7">
+        <v>1000</v>
+      </c>
+      <c r="G19" s="7">
+        <v>1000</v>
+      </c>
+      <c r="H19" s="7">
+        <v>1000</v>
+      </c>
+      <c r="I19" s="6"/>
+    </row>
+    <row r="20" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="19"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="E20" s="8">
+        <v>0</v>
+      </c>
+      <c r="F20" s="7">
+        <v>1000</v>
+      </c>
+      <c r="G20" s="7">
+        <v>1000</v>
+      </c>
+      <c r="H20" s="7">
+        <v>1000</v>
+      </c>
+      <c r="I20" s="6"/>
+    </row>
+    <row r="21" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="19"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E21" s="8">
+        <v>0</v>
+      </c>
+      <c r="F21" s="7">
+        <v>1000</v>
+      </c>
+      <c r="G21" s="7">
+        <v>1000</v>
+      </c>
+      <c r="H21" s="7">
+        <v>1000</v>
+      </c>
+      <c r="I21" s="6"/>
+    </row>
+    <row r="22" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="19"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="E22" s="8">
+        <v>0</v>
+      </c>
+      <c r="F22" s="7">
+        <v>1000</v>
+      </c>
+      <c r="G22" s="7">
+        <v>1000</v>
+      </c>
+      <c r="H22" s="7">
+        <v>1000</v>
+      </c>
+      <c r="I22" s="6"/>
+    </row>
+    <row r="23" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="19"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="E23" s="8">
+        <v>0</v>
+      </c>
+      <c r="F23" s="7">
+        <v>1000</v>
+      </c>
+      <c r="G23" s="7">
+        <v>1000</v>
+      </c>
+      <c r="H23" s="7">
+        <v>1000</v>
+      </c>
+      <c r="I23" s="6"/>
+    </row>
+    <row r="24" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="19"/>
+      <c r="B24" s="4"/>
+      <c r="C24" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E24" s="8">
+        <v>0</v>
+      </c>
+      <c r="F24" s="7">
+        <v>1000</v>
+      </c>
+      <c r="G24" s="7">
+        <v>1000</v>
+      </c>
+      <c r="H24" s="7">
+        <v>1000</v>
+      </c>
+      <c r="I24" s="6"/>
+    </row>
+    <row r="25" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="20"/>
+      <c r="B25" s="5"/>
+      <c r="C25" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E25" s="8">
+        <v>276</v>
+      </c>
+      <c r="F25" s="8">
+        <v>0</v>
+      </c>
+      <c r="G25" s="8">
+        <v>276</v>
+      </c>
+      <c r="H25" s="8">
+        <v>276</v>
+      </c>
+      <c r="I25" s="10"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
-  </conditionalFormatting>
+  <mergeCells count="1">
+    <mergeCell ref="A2:A25"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>